--- a/documentation/bom/project costed bom.xlsx
+++ b/documentation/bom/project costed bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lola\Desktop\myoelectric hand project\helping files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B28D74-2E89-4F04-9F3E-17F40491385B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1189233F-A66C-485E-BE75-D9AEE488FC07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{420CDE9A-48D4-4FB1-A9C9-FF6CDA179545}"/>
   </bookViews>
@@ -496,7 +496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -527,6 +527,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1370,29 +1373,29 @@
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="25"/>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="28"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="23.4" x14ac:dyDescent="0.55000000000000004">
@@ -1448,7 +1451,9 @@
       <c r="D6" s="21">
         <v>1850</v>
       </c>
-      <c r="E6" s="21"/>
+      <c r="E6" s="22">
+        <v>36.417322834645702</v>
+      </c>
       <c r="F6" s="21" t="s">
         <v>24</v>
       </c>
@@ -1473,7 +1478,9 @@
       <c r="D7" s="21">
         <v>600</v>
       </c>
-      <c r="E7" s="21"/>
+      <c r="E7" s="22">
+        <v>11.811023622047244</v>
+      </c>
       <c r="F7" s="21" t="s">
         <v>13</v>
       </c>
@@ -1498,7 +1505,9 @@
       <c r="D8" s="21">
         <v>250</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E8" s="22">
+        <v>4.9212598425196852</v>
+      </c>
       <c r="F8" s="21" t="s">
         <v>11</v>
       </c>
@@ -1521,7 +1530,9 @@
       <c r="D9" s="21">
         <v>300</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="22">
+        <v>5.9055118110236222</v>
+      </c>
       <c r="F9" s="21" t="s">
         <v>13</v>
       </c>
@@ -1544,7 +1555,9 @@
       <c r="D10" s="21">
         <v>230</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="22">
+        <v>4.5275590551181102</v>
+      </c>
       <c r="F10" s="21" t="s">
         <v>12</v>
       </c>
@@ -1567,7 +1580,9 @@
       <c r="D11" s="21">
         <v>100</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="22">
+        <v>1.9685039370078741</v>
+      </c>
       <c r="F11" s="21" t="s">
         <v>12</v>
       </c>
@@ -1592,7 +1607,9 @@
       <c r="D12" s="21">
         <v>420</v>
       </c>
-      <c r="E12" s="21"/>
+      <c r="E12" s="22">
+        <v>8.2677165354330722</v>
+      </c>
       <c r="F12" s="21" t="s">
         <v>25</v>
       </c>
@@ -1617,7 +1634,9 @@
       <c r="D13" s="21">
         <v>185</v>
       </c>
-      <c r="E13" s="21"/>
+      <c r="E13" s="22">
+        <v>3.6417322834645671</v>
+      </c>
       <c r="F13" s="21" t="s">
         <v>12</v>
       </c>
